--- a/Team-Data/2007-08/3-7-2007-08.xlsx
+++ b/Team-Data/2007-08/3-7-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
         <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>0.41</v>
+        <v>0.417</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
@@ -691,10 +758,10 @@
         <v>12.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.339</v>
+        <v>0.34</v>
       </c>
       <c r="O2" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="P2" t="n">
         <v>27.5</v>
@@ -706,10 +773,10 @@
         <v>12.6</v>
       </c>
       <c r="S2" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T2" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U2" t="n">
         <v>21.3</v>
@@ -727,19 +794,19 @@
         <v>5.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB2" t="n">
         <v>95.90000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.9</v>
+        <v>-2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
         <v>20</v>
@@ -751,7 +818,7 @@
         <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI2" t="n">
         <v>27</v>
@@ -769,7 +836,7 @@
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO2" t="n">
         <v>5</v>
@@ -778,7 +845,7 @@
         <v>6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR2" t="n">
         <v>4</v>
@@ -805,13 +872,13 @@
         <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
         <v>9</v>
       </c>
       <c r="BB2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
@@ -861,7 +928,7 @@
         <v>36</v>
       </c>
       <c r="J3" t="n">
-        <v>76</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0.474</v>
@@ -870,55 +937,55 @@
         <v>7.4</v>
       </c>
       <c r="M3" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.385</v>
+        <v>0.386</v>
       </c>
       <c r="O3" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="P3" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.769</v>
+        <v>0.766</v>
       </c>
       <c r="R3" t="n">
         <v>9.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="T3" t="n">
-        <v>41.3</v>
+        <v>41</v>
       </c>
       <c r="U3" t="n">
         <v>22.1</v>
       </c>
       <c r="V3" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y3" t="n">
         <v>4.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.4</v>
+        <v>100.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>28</v>
@@ -945,7 +1012,7 @@
         <v>4</v>
       </c>
       <c r="AL3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM3" t="n">
         <v>11</v>
@@ -954,13 +1021,13 @@
         <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>26</v>
@@ -969,19 +1036,19 @@
         <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU3" t="n">
         <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
         <v>17</v>
@@ -993,7 +1060,7 @@
         <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>0.371</v>
+        <v>0.361</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J4" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L4" t="n">
         <v>6.3</v>
@@ -1055,22 +1122,22 @@
         <v>17.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.363</v>
+        <v>0.36</v>
       </c>
       <c r="O4" t="n">
         <v>18.4</v>
       </c>
       <c r="P4" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.71</v>
+        <v>0.711</v>
       </c>
       <c r="R4" t="n">
         <v>11.3</v>
       </c>
       <c r="S4" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T4" t="n">
         <v>40.8</v>
@@ -1094,31 +1161,31 @@
         <v>22.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.7</v>
+        <v>-5</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ4" t="n">
         <v>18</v>
@@ -1136,7 +1203,7 @@
         <v>13</v>
       </c>
       <c r="AO4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
@@ -1148,10 +1215,10 @@
         <v>17</v>
       </c>
       <c r="AS4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT4" t="n">
         <v>25</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>24</v>
       </c>
       <c r="AU4" t="n">
         <v>18</v>
@@ -1163,7 +1230,7 @@
         <v>14</v>
       </c>
       <c r="AX4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
@@ -1175,10 +1242,10 @@
         <v>15</v>
       </c>
       <c r="BB4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -1207,85 +1274,85 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
         <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>0.403</v>
+        <v>0.41</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="J5" t="n">
         <v>84.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.427</v>
+        <v>0.429</v>
       </c>
       <c r="L5" t="n">
         <v>5.5</v>
       </c>
       <c r="M5" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.348</v>
+        <v>0.35</v>
       </c>
       <c r="O5" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.744</v>
+        <v>0.741</v>
       </c>
       <c r="R5" t="n">
         <v>13.5</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T5" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U5" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V5" t="n">
         <v>14.7</v>
       </c>
       <c r="W5" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
         <v>96.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.7</v>
+        <v>-2.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>20</v>
@@ -1297,10 +1364,10 @@
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1312,19 +1379,19 @@
         <v>22</v>
       </c>
       <c r="AM5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO5" t="n">
         <v>18</v>
       </c>
-      <c r="AO5" t="n">
-        <v>16</v>
-      </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1333,7 +1400,7 @@
         <v>17</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU5" t="n">
         <v>12</v>
@@ -1342,7 +1409,7 @@
         <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
         <v>8</v>
@@ -1351,16 +1418,16 @@
         <v>28</v>
       </c>
       <c r="AZ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB5" t="n">
         <v>19</v>
       </c>
-      <c r="BA5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>20</v>
-      </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1482,13 +1549,13 @@
         <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ6" t="n">
         <v>11</v>
       </c>
       <c r="AK6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
         <v>12</v>
@@ -1512,7 +1579,7 @@
         <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT6" t="n">
         <v>5</v>
@@ -1527,7 +1594,7 @@
         <v>15</v>
       </c>
       <c r="AX6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
@@ -1661,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>17</v>
@@ -1670,22 +1737,22 @@
         <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM7" t="n">
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -1718,7 +1785,7 @@
         <v>22</v>
       </c>
       <c r="BA7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
         <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.607</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,67 +1838,67 @@
         <v>39.1</v>
       </c>
       <c r="J8" t="n">
-        <v>85.3</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L8" t="n">
         <v>6.5</v>
       </c>
       <c r="M8" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="O8" t="n">
         <v>22.9</v>
       </c>
       <c r="P8" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.753</v>
+        <v>0.755</v>
       </c>
       <c r="R8" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="S8" t="n">
         <v>32.7</v>
       </c>
       <c r="T8" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U8" t="n">
         <v>23.8</v>
       </c>
       <c r="V8" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W8" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="Y8" t="n">
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="AB8" t="n">
         <v>107.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
@@ -1849,19 +1916,19 @@
         <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK8" t="n">
         <v>11</v>
       </c>
       <c r="AL8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM8" t="n">
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,7 +1940,7 @@
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS8" t="n">
         <v>3</v>
@@ -1885,7 +1952,7 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1897,7 +1964,7 @@
         <v>18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
         <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>0.726</v>
+        <v>0.721</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
@@ -1953,28 +2020,28 @@
         <v>36.5</v>
       </c>
       <c r="J9" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="K9" t="n">
         <v>0.457</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M9" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O9" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P9" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R9" t="n">
         <v>11.6</v>
@@ -1983,10 +2050,10 @@
         <v>29.5</v>
       </c>
       <c r="T9" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U9" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V9" t="n">
         <v>11.5</v>
@@ -2001,19 +2068,19 @@
         <v>3.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,10 +2095,10 @@
         <v>29</v>
       </c>
       <c r="AI9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
         <v>13</v>
@@ -2043,7 +2110,7 @@
         <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO9" t="n">
         <v>13</v>
@@ -2052,7 +2119,7 @@
         <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
         <v>14</v>
@@ -2061,7 +2128,7 @@
         <v>24</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
         <v>8</v>
@@ -2076,7 +2143,7 @@
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ9" t="n">
         <v>16</v>
@@ -2085,10 +2152,10 @@
         <v>22</v>
       </c>
       <c r="BB9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10" t="n">
         <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>0.623</v>
+        <v>0.617</v>
       </c>
       <c r="H10" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="J10" t="n">
-        <v>89.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.463</v>
+        <v>0.461</v>
       </c>
       <c r="L10" t="n">
         <v>9.6</v>
@@ -2147,25 +2214,25 @@
         <v>27.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O10" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P10" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q10" t="n">
         <v>0.748</v>
       </c>
       <c r="R10" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S10" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T10" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U10" t="n">
         <v>23</v>
@@ -2174,7 +2241,7 @@
         <v>13.4</v>
       </c>
       <c r="W10" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="X10" t="n">
         <v>4.6</v>
@@ -2186,16 +2253,16 @@
         <v>23.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>110.9</v>
+        <v>110.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2237,13 +2304,13 @@
         <v>18</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
         <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
@@ -2258,19 +2325,19 @@
         <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ10" t="n">
         <v>27</v>
       </c>
       <c r="BA10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
       </c>
       <c r="BC10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>5</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF11" t="n">
         <v>6</v>
@@ -2389,13 +2456,13 @@
         <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
         <v>12</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK11" t="n">
         <v>16</v>
@@ -2404,7 +2471,7 @@
         <v>11</v>
       </c>
       <c r="AM11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN11" t="n">
         <v>20</v>
@@ -2413,13 +2480,13 @@
         <v>28</v>
       </c>
       <c r="AP11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS11" t="n">
         <v>5</v>
@@ -2446,7 +2513,7 @@
         <v>5</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB11" t="n">
         <v>17</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
@@ -2571,13 +2638,13 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
         <v>9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK12" t="n">
         <v>27</v>
@@ -2604,7 +2671,7 @@
         <v>18</v>
       </c>
       <c r="AS12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
@@ -2622,19 +2689,19 @@
         <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" t="n">
         <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J13" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L13" t="n">
         <v>4.2</v>
@@ -2693,28 +2760,28 @@
         <v>12.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.331</v>
+        <v>0.333</v>
       </c>
       <c r="O13" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="P13" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="Q13" t="n">
         <v>0.787</v>
       </c>
       <c r="R13" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S13" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T13" t="n">
         <v>40.2</v>
       </c>
       <c r="U13" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V13" t="n">
         <v>14.4</v>
@@ -2726,19 +2793,19 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.8</v>
+        <v>94</v>
       </c>
       <c r="AC13" t="n">
-        <v>-5.8</v>
+        <v>-5.3</v>
       </c>
       <c r="AD13" t="n">
         <v>28</v>
@@ -2747,13 +2814,13 @@
         <v>25</v>
       </c>
       <c r="AF13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG13" t="n">
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2762,7 +2829,7 @@
         <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
         <v>27</v>
@@ -2783,7 +2850,7 @@
         <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS13" t="n">
         <v>16</v>
@@ -2795,16 +2862,16 @@
         <v>15</v>
       </c>
       <c r="AV13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
         <v>19</v>
       </c>
       <c r="AX13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
         <v>20</v>
@@ -2813,7 +2880,7 @@
         <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -2845,55 +2912,55 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F14" t="n">
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>0.71</v>
+        <v>0.705</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J14" t="n">
         <v>82.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.479</v>
+        <v>0.478</v>
       </c>
       <c r="L14" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M14" t="n">
         <v>20.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.372</v>
+        <v>0.367</v>
       </c>
       <c r="O14" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="P14" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R14" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S14" t="n">
         <v>33.6</v>
       </c>
       <c r="T14" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="U14" t="n">
         <v>23.7</v>
@@ -2902,40 +2969,40 @@
         <v>14.7</v>
       </c>
       <c r="W14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
         <v>20.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2947,22 +3014,22 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM14" t="n">
         <v>9</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>8</v>
       </c>
       <c r="AN14" t="n">
         <v>10</v>
       </c>
       <c r="AO14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
         <v>20</v>
@@ -2989,16 +3056,16 @@
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>28</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG15" t="n">
         <v>28</v>
@@ -3123,7 +3190,7 @@
         <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK15" t="n">
         <v>17</v>
@@ -3156,7 +3223,7 @@
         <v>19</v>
       </c>
       <c r="AU15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV15" t="n">
         <v>28</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
         <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>0.183</v>
+        <v>0.186</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,7 +3294,7 @@
         <v>35.4</v>
       </c>
       <c r="J16" t="n">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="K16" t="n">
         <v>0.455</v>
@@ -3236,31 +3303,31 @@
         <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.344</v>
+        <v>0.346</v>
       </c>
       <c r="O16" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P16" t="n">
         <v>24.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.724</v>
+        <v>0.723</v>
       </c>
       <c r="R16" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T16" t="n">
         <v>38.1</v>
       </c>
       <c r="U16" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V16" t="n">
         <v>15</v>
@@ -3269,22 +3336,22 @@
         <v>7.3</v>
       </c>
       <c r="X16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y16" t="n">
         <v>3.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA16" t="n">
         <v>21.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>-7.9</v>
+        <v>-7.4</v>
       </c>
       <c r="AD16" t="n">
         <v>28</v>
@@ -3293,7 +3360,7 @@
         <v>30</v>
       </c>
       <c r="AF16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG16" t="n">
         <v>30</v>
@@ -3317,13 +3384,13 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AQ16" t="n">
         <v>26</v>
@@ -3338,10 +3405,10 @@
         <v>30</v>
       </c>
       <c r="AU16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW16" t="n">
         <v>18</v>
@@ -3353,7 +3420,7 @@
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
         <v>16</v>
@@ -3362,7 +3429,7 @@
         <v>29</v>
       </c>
       <c r="BC16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E17" t="n">
         <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>0.371</v>
+        <v>0.377</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3412,7 +3479,7 @@
         <v>81.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L17" t="n">
         <v>5.5</v>
@@ -3421,7 +3488,7 @@
         <v>16.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O17" t="n">
         <v>17.6</v>
@@ -3439,49 +3506,49 @@
         <v>28.7</v>
       </c>
       <c r="T17" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U17" t="n">
         <v>21.1</v>
       </c>
       <c r="V17" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W17" t="n">
         <v>6.5</v>
       </c>
       <c r="X17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y17" t="n">
         <v>5.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA17" t="n">
         <v>20.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.2</v>
+        <v>-6.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE17" t="n">
         <v>23</v>
       </c>
       <c r="AF17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
         <v>23</v>
       </c>
       <c r="AH17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI17" t="n">
         <v>18</v>
@@ -3496,19 +3563,19 @@
         <v>23</v>
       </c>
       <c r="AM17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR17" t="n">
         <v>6</v>
@@ -3517,7 +3584,7 @@
         <v>30</v>
       </c>
       <c r="AT17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU17" t="n">
         <v>19</v>
@@ -3529,13 +3596,13 @@
         <v>23</v>
       </c>
       <c r="AX17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY17" t="n">
         <v>20</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA17" t="n">
         <v>19</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
         <v>48</v>
       </c>
       <c r="G18" t="n">
-        <v>0.213</v>
+        <v>0.2</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
       </c>
       <c r="I18" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J18" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L18" t="n">
         <v>5.4</v>
@@ -3603,28 +3670,28 @@
         <v>15.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="O18" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="P18" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="R18" t="n">
         <v>12.1</v>
       </c>
       <c r="S18" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T18" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U18" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V18" t="n">
         <v>15.3</v>
@@ -3639,19 +3706,19 @@
         <v>5.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.5</v>
+        <v>93.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.6</v>
+        <v>-7.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3666,22 +3733,22 @@
         <v>28</v>
       </c>
       <c r="AI18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ18" t="n">
         <v>8</v>
       </c>
       <c r="AK18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL18" t="n">
         <v>24</v>
       </c>
       <c r="AM18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3696,19 +3763,19 @@
         <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AT18" t="n">
         <v>18</v>
       </c>
       <c r="AU18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3726,7 +3793,7 @@
         <v>30</v>
       </c>
       <c r="BC18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" t="n">
         <v>26</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>0.419</v>
+        <v>0.426</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="J19" t="n">
-        <v>78.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L19" t="n">
         <v>5.9</v>
@@ -3785,25 +3852,25 @@
         <v>17.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.341</v>
+        <v>0.344</v>
       </c>
       <c r="O19" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="P19" t="n">
-        <v>27.1</v>
+        <v>27.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.727</v>
+        <v>0.726</v>
       </c>
       <c r="R19" t="n">
         <v>11.4</v>
       </c>
       <c r="S19" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T19" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U19" t="n">
         <v>23.5</v>
@@ -3824,16 +3891,16 @@
         <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="AB19" t="n">
         <v>94</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5</v>
+        <v>-4.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
@@ -3845,7 +3912,7 @@
         <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3854,7 +3921,7 @@
         <v>28</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL19" t="n">
         <v>19</v>
@@ -3863,22 +3930,22 @@
         <v>17</v>
       </c>
       <c r="AN19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
         <v>9</v>
@@ -3890,7 +3957,7 @@
         <v>25</v>
       </c>
       <c r="AW19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
@@ -3905,10 +3972,10 @@
         <v>8</v>
       </c>
       <c r="BB19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20" t="n">
         <v>19</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3955,28 +4022,28 @@
         <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L20" t="n">
         <v>7.9</v>
       </c>
       <c r="M20" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.39</v>
+        <v>0.392</v>
       </c>
       <c r="O20" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="P20" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="R20" t="n">
         <v>11.7</v>
@@ -4003,19 +4070,19 @@
         <v>4.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
         <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.4</v>
+        <v>100.3</v>
       </c>
       <c r="AC20" t="n">
         <v>5.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
         <v>5</v>
@@ -4042,7 +4109,7 @@
         <v>5</v>
       </c>
       <c r="AM20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN20" t="n">
         <v>2</v>
@@ -4054,13 +4121,13 @@
         <v>30</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR20" t="n">
         <v>13</v>
       </c>
       <c r="AS20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT20" t="n">
         <v>10</v>
@@ -4072,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX20" t="n">
         <v>28</v>
@@ -4081,16 +4148,16 @@
         <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA20" t="n">
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E21" t="n">
         <v>18</v>
       </c>
       <c r="F21" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>0.29</v>
+        <v>0.295</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
@@ -4149,7 +4216,7 @@
         <v>17.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.336</v>
+        <v>0.335</v>
       </c>
       <c r="O21" t="n">
         <v>19</v>
@@ -4158,19 +4225,19 @@
         <v>26.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.727</v>
+        <v>0.726</v>
       </c>
       <c r="R21" t="n">
         <v>12.2</v>
       </c>
       <c r="S21" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U21" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="V21" t="n">
         <v>15.2</v>
@@ -4194,10 +4261,10 @@
         <v>95.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.3</v>
+        <v>-6.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4209,7 +4276,7 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI21" t="n">
         <v>28</v>
@@ -4218,7 +4285,7 @@
         <v>19</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
         <v>21</v>
@@ -4239,10 +4306,10 @@
         <v>25</v>
       </c>
       <c r="AR21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT21" t="n">
         <v>16</v>
@@ -4263,7 +4330,7 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
         <v>17</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF22" t="n">
         <v>9</v>
@@ -4421,19 +4488,19 @@
         <v>22</v>
       </c>
       <c r="AR22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS22" t="n">
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU22" t="n">
         <v>23</v>
       </c>
       <c r="AV22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW22" t="n">
         <v>26</v>
@@ -4445,7 +4512,7 @@
         <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -4483,43 +4550,43 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F23" t="n">
         <v>33</v>
       </c>
       <c r="G23" t="n">
-        <v>0.468</v>
+        <v>0.459</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J23" t="n">
-        <v>80.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
         <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.32</v>
+        <v>0.318</v>
       </c>
       <c r="O23" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P23" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q23" t="n">
         <v>0.702</v>
@@ -4534,13 +4601,13 @@
         <v>42</v>
       </c>
       <c r="U23" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V23" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W23" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X23" t="n">
         <v>4.9</v>
@@ -4549,19 +4616,19 @@
         <v>4.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
         <v>17</v>
@@ -4582,7 +4649,7 @@
         <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4597,7 +4664,7 @@
         <v>22</v>
       </c>
       <c r="AP23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4612,28 +4679,28 @@
         <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
         <v>5</v>
       </c>
       <c r="AX23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY23" t="n">
         <v>16</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E24" t="n">
         <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G24" t="n">
-        <v>0.645</v>
+        <v>0.656</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4692,28 +4759,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="O24" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P24" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.789</v>
+        <v>0.792</v>
       </c>
       <c r="R24" t="n">
         <v>8.6</v>
       </c>
       <c r="S24" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="T24" t="n">
-        <v>40.7</v>
+        <v>40.9</v>
       </c>
       <c r="U24" t="n">
         <v>26.7</v>
@@ -4725,34 +4792,34 @@
         <v>6.9</v>
       </c>
       <c r="X24" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Y24" t="n">
         <v>3.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.5</v>
+        <v>109.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF24" t="n">
         <v>7</v>
       </c>
       <c r="AG24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH24" t="n">
         <v>20</v>
@@ -4776,31 +4843,31 @@
         <v>4</v>
       </c>
       <c r="AO24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4812,7 +4879,7 @@
         <v>6</v>
       </c>
       <c r="BA24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -4847,43 +4914,43 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
         <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>0.516</v>
+        <v>0.508</v>
       </c>
       <c r="H25" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I25" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J25" t="n">
         <v>79</v>
       </c>
       <c r="K25" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L25" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M25" t="n">
         <v>17</v>
       </c>
       <c r="N25" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="O25" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P25" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q25" t="n">
         <v>0.766</v>
@@ -4895,7 +4962,7 @@
         <v>29.8</v>
       </c>
       <c r="T25" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -4910,22 +4977,22 @@
         <v>4.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z25" t="n">
         <v>20.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4949,31 +5016,31 @@
         <v>18</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM25" t="n">
         <v>18</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP25" t="n">
         <v>23</v>
       </c>
-      <c r="AP25" t="n">
-        <v>24</v>
-      </c>
       <c r="AQ25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU25" t="n">
         <v>20</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E26" t="n">
         <v>27</v>
       </c>
       <c r="F26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G26" t="n">
-        <v>0.435</v>
+        <v>0.443</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J26" t="n">
-        <v>79.8</v>
+        <v>80</v>
       </c>
       <c r="K26" t="n">
         <v>0.457</v>
@@ -5056,28 +5123,28 @@
         <v>6.4</v>
       </c>
       <c r="M26" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N26" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O26" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="P26" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="R26" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S26" t="n">
         <v>29.8</v>
       </c>
       <c r="T26" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U26" t="n">
         <v>19</v>
@@ -5104,10 +5171,10 @@
         <v>101.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,13 +5186,13 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
         <v>12</v>
@@ -5146,7 +5213,7 @@
         <v>5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR26" t="n">
         <v>22</v>
@@ -5155,7 +5222,7 @@
         <v>19</v>
       </c>
       <c r="AT26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU26" t="n">
         <v>28</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
         <v>43</v>
       </c>
       <c r="F27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G27" t="n">
-        <v>0.705</v>
+        <v>0.717</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
@@ -5238,34 +5305,34 @@
         <v>7.8</v>
       </c>
       <c r="M27" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="O27" t="n">
         <v>16.9</v>
       </c>
       <c r="P27" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S27" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T27" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="U27" t="n">
         <v>21.4</v>
       </c>
       <c r="V27" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W27" t="n">
         <v>6.6</v>
@@ -5274,37 +5341,37 @@
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="AA27" t="n">
         <v>20.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>96</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG27" t="n">
         <v>3</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>4</v>
       </c>
       <c r="AH27" t="n">
         <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ27" t="n">
         <v>27</v>
@@ -5325,10 +5392,10 @@
         <v>26</v>
       </c>
       <c r="AP27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR27" t="n">
         <v>24</v>
@@ -5355,7 +5422,7 @@
         <v>12</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA27" t="n">
         <v>24</v>
@@ -5364,7 +5431,7 @@
         <v>21</v>
       </c>
       <c r="BC27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E28" t="n">
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G28" t="n">
-        <v>0.258</v>
+        <v>0.262</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5411,7 +5478,7 @@
         <v>37.7</v>
       </c>
       <c r="J28" t="n">
-        <v>85.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="K28" t="n">
         <v>0.442</v>
@@ -5423,31 +5490,31 @@
         <v>12</v>
       </c>
       <c r="N28" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="O28" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P28" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="R28" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S28" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="T28" t="n">
-        <v>45.3</v>
+        <v>45.5</v>
       </c>
       <c r="U28" t="n">
         <v>21.5</v>
       </c>
       <c r="V28" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W28" t="n">
         <v>6.4</v>
@@ -5459,19 +5526,19 @@
         <v>5.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>-7.7</v>
+        <v>-7.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5483,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="AH28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5501,16 +5568,16 @@
         <v>29</v>
       </c>
       <c r="AN28" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP28" t="n">
         <v>25</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
         <v>12</v>
@@ -5537,16 +5604,16 @@
         <v>26</v>
       </c>
       <c r="AZ28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB28" t="n">
         <v>18</v>
       </c>
       <c r="BC28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -5575,70 +5642,70 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
         <v>33</v>
       </c>
       <c r="F29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>0.541</v>
+        <v>0.55</v>
       </c>
       <c r="H29" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J29" t="n">
-        <v>81.5</v>
+        <v>81.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="L29" t="n">
         <v>7.5</v>
       </c>
       <c r="M29" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.407</v>
+        <v>0.409</v>
       </c>
       <c r="O29" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P29" t="n">
         <v>20.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T29" t="n">
         <v>40.4</v>
       </c>
       <c r="U29" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V29" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X29" t="n">
         <v>4</v>
       </c>
       <c r="Y29" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z29" t="n">
         <v>19.9</v>
@@ -5647,31 +5714,31 @@
         <v>18.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
       </c>
       <c r="AF29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG29" t="n">
         <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK29" t="n">
         <v>6</v>
@@ -5698,7 +5765,7 @@
         <v>25</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
         <v>26</v>
@@ -5710,16 +5777,16 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY29" t="n">
         <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA29" t="n">
         <v>29</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -5757,58 +5824,58 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E30" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F30" t="n">
         <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>0.651</v>
+        <v>0.645</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="J30" t="n">
         <v>80.5</v>
       </c>
       <c r="K30" t="n">
-        <v>0.495</v>
+        <v>0.494</v>
       </c>
       <c r="L30" t="n">
         <v>4.5</v>
       </c>
       <c r="M30" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O30" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="P30" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R30" t="n">
         <v>11.4</v>
       </c>
       <c r="S30" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T30" t="n">
         <v>40.9</v>
       </c>
       <c r="U30" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="V30" t="n">
         <v>15.1</v>
@@ -5826,25 +5893,25 @@
         <v>24.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>105.9</v>
+        <v>105.5</v>
       </c>
       <c r="AC30" t="n">
         <v>5.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
@@ -5868,22 +5935,22 @@
         <v>14</v>
       </c>
       <c r="AO30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ30" t="n">
         <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F31" t="n">
         <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>0.492</v>
+        <v>0.483</v>
       </c>
       <c r="H31" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J31" t="n">
         <v>82</v>
       </c>
       <c r="K31" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L31" t="n">
         <v>6.5</v>
@@ -5969,37 +6036,37 @@
         <v>19.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="O31" t="n">
         <v>19.3</v>
       </c>
       <c r="P31" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.794</v>
+        <v>0.792</v>
       </c>
       <c r="R31" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S31" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T31" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U31" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="V31" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W31" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X31" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y31" t="n">
         <v>4.3</v>
@@ -6011,13 +6078,13 @@
         <v>20.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC31" t="n">
         <v>-0.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6029,16 +6096,16 @@
         <v>16</v>
       </c>
       <c r="AH31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AJ31" t="n">
         <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>13</v>
@@ -6047,7 +6114,7 @@
         <v>12</v>
       </c>
       <c r="AN31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6062,7 +6129,7 @@
         <v>5</v>
       </c>
       <c r="AS31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT31" t="n">
         <v>14</v>
@@ -6077,7 +6144,7 @@
         <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
         <v>8</v>
@@ -6089,7 +6156,7 @@
         <v>25</v>
       </c>
       <c r="BB31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-7-2007-08</t>
+          <t>2008-03-07</t>
         </is>
       </c>
     </row>
